--- a/China NEA/review_workbooks/2025-08-04_2025年上半年光伏发电建设情况---国家能源局_review.xlsx
+++ b/China NEA/review_workbooks/2025-08-04_2025年上半年光伏发电建设情况---国家能源局_review.xlsx
@@ -428,1931 +428,999 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
       <c r="B1" t="n">
-        <v>0</v>
+        <v>21161</v>
       </c>
       <c r="C1" t="n">
+        <v>9880</v>
+      </c>
+      <c r="D1" t="n">
+        <v>11281</v>
+      </c>
+      <c r="E1" t="n">
+        <v>2563</v>
+      </c>
+      <c r="F1" t="n">
+        <v>109851</v>
+      </c>
+      <c r="G1" t="n">
+        <v>60595</v>
+      </c>
+      <c r="H1" t="n">
+        <v>49256</v>
+      </c>
+      <c r="I1" t="n">
+        <v>17966</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>143</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>948.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>515.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>948.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>487.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>461.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8072.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4703.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3369.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1958.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1220.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>728.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>492.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4749.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3332.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1416.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>687.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D6" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4996.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4566.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>430.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>169.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>67</v>
+      </c>
+      <c r="D7" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1495.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>609.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>886.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>419.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>687.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>427.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>259.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>151.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>51</v>
+      </c>
+      <c r="F9" t="n">
+        <v>858.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>358</v>
+      </c>
+      <c r="I9" t="n">
+        <v>140.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>119</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>545.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>490.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2207.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>831.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1376.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8372.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2426.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5945.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1998.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1219.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1049.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5947.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1003.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4943.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1063.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>238.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5375.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1556.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3818.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1745.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1589.8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1482.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>569.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>204.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2769.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1393.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1375.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>750.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1504.9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>908.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9118.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3189.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5929.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2878.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>718.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>670.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>199.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5067.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>677.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4389.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2507.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>772.9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4282.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2204.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2078.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>345.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>667.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>528.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>234.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2540.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>624.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1915.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1135.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1559</v>
+      </c>
+      <c r="C20" t="n">
+        <v>407.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1151.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5742.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1563.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4179</v>
+      </c>
+      <c r="I20" t="n">
+        <v>622.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>663.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2792</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1275.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1516.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>956.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>607.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>192.1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>40</v>
+      </c>
+      <c r="F23" t="n">
+        <v>501.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>488</v>
+      </c>
+      <c r="C24" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>330.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1570.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1047.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>523.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>663.9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>545.1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2649.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2421.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>228.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>137.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1186.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5084.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4619.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>465</v>
+      </c>
+      <c r="I26" t="n">
+        <v>125.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>511.9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>506.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3996.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2728.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1267.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>568.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3535.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3285.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>249.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E30" t="n">
         <v>1</v>
       </c>
-      <c r="D1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>其中：分布式光
-伏
-其中：</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>其中：分布式光
-伏
-其中：</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>其中：分布式光
-伏
-其中：</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>其中：分布式光
-伏
-其中：</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>其中：分布式光
-伏
-其中：</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>其中：</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量
-其中：分布式光
-其中：
-伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>其中：分布式光
-伏
-其中：</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>其中：</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>站</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>户用光</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>站</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>户用光</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>伏</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21161</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9880</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>11281</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2563</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>109851</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>60595</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>49256</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>17966</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>181.3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>173.2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>224.1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>948.3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>432.5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>515.8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>948.7</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>487.3</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>461.5</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>122.3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8072.9</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4703.1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3369.8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1958.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1220.6</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>728.1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>492.5</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4749.4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3332.6</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1416.8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>687.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>185.3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>121.3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4996.1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4566.1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>430.1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>169.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>281.4</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>214.4</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1495.3</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>609.1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>886.2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>419.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>44.2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>687.5</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>427.7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>259.7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>151.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>142.2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>30.2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>112.1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>858.5</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>500.5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>358.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>140.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>134.1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>545.5</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>490.6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2207.4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>831.3</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1376.1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>316.4</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8372.1</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2426.3</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5945.7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1998.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1219.7</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>169.8</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1049.9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>132.9</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>5947.2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1003.7</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4943.5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>585.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1063.8</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>144.9</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>918.9</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>238.2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>5375.1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1556.4</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3818.7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1745.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>331.4</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>300.9</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1589.8</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>107.1</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1482.7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>569.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>204.1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>186.5</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2769.4</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1393.5</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1375.9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>750.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1504.9</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>596.4</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>908.5</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>114.9</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>9118.4</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>3189.3</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5929.1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2878.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>718.1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>670.6</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>199.3</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>5067.2</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>677.5</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4389.7</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2507.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>772.9</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>716.4</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>4282.8</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2204.3</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2078.6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>345.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>667.1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>138.7</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>528.4</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>234.7</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2540.5</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>624.8</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1915.7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>1135.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1559.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>407.9</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1151.1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>265.2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>5742.2</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1563.2</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4179.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>622.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>663.2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>359.9</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>303.4</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2792.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1275.3</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1516.7</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>215.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>133.2</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>956.4</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>607.5</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>348.9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>192.1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>157.9</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>501.8</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>140.4</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>361.4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>488.0</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>157.9</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>330.1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>59.7</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1570.3</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1047.2</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>523.1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>83.6</t>
-        </is>
+      <c r="F30" t="n">
+        <v>3864.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3821.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6.3</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>663.9</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>545.1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>118.8</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2649.5</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2421.2</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>228.2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>137.8</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>792.2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>714</v>
+      </c>
+      <c r="D31" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3416.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3163.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1361.4</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1186.3</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>175.1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>5084.4</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>4619.4</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>465.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>125.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>84.1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>511.9</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>506.5</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>563.3</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>204.5</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>358.7</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>135.6</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>3996.4</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2728.6</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1267.8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>568.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>396.3</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>330.8</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>3535.1</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3285.7</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>249.5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>222.3</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>217.5</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>3864.4</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>3821.7</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>792.2</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>714.0</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3416.2</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3163.3</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>252.9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>新疆</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1959.5</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1950.7</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>7633.5</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>7598.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1959.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1950.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7633.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7598</v>
+      </c>
+      <c r="H32" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -2400,11 +1468,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>省(区、市)</t>
@@ -2425,11 +1489,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量其中：分布式光其中：伏集中式其中：光伏电</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>2025年上半年新增并网容量</t>
@@ -2450,11 +1510,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量其中：分布式光其中：伏集中式其中：光伏电其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2025年上半年新增并网容量_其中：集中式光伏电站</t>
@@ -2475,11 +1531,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量其中：分布式光其中：伏集中式其中：光伏电其中：分布式光伏其中：</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2025年上半年新增并网容量_其中：分布式光伏</t>
@@ -2500,11 +1552,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025上半年新增并网容量其中：分布式光其中：伏集中式其中：光伏电其中：分布式光伏其中：其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2025年上半年新增并网容量_其中：户用光伏</t>
@@ -2525,11 +1573,7 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量其中：分布式光其中：伏集中式其中：光伏电</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>截至2025年6月底累计并网容量</t>
@@ -2550,11 +1594,7 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量其中：分布式光其中：伏集中式其中：光伏电其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>截至2025年6月底累计并网容量_其中：集中式光伏电站</t>
@@ -2575,11 +1615,7 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量其中：分布式光其中：伏集中式其中：光伏电其中：分布式光伏其中：</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>截至2025年6月底累计并网容量_其中：分布式光伏</t>
@@ -2600,11 +1636,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>截至2025年6月底累计并网容量其中：分布式光其中：伏集中式其中：光伏电其中：分布式光伏其中：其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>截至2025年6月底累计并网容量_其中：户用光伏</t>
